--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -85,250 +85,169 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ABURTO</t>
+  </si>
+  <si>
+    <t>CESMA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
   </si>
   <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>CESMA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>VAS</t>
   </si>
   <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VALLEJOS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>SALMERON</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
     <t>XOCHICALE</t>
   </si>
   <si>
-    <t>ALEXANDRO</t>
-  </si>
-  <si>
-    <t>CARMEN STEFANY</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
+    <t>CORDERO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL OSWALDO</t>
+  </si>
+  <si>
+    <t>MARTIN ERNESTO</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS PABLO</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
   </si>
   <si>
     <t>ROSMELY LEILANI</t>
   </si>
   <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>ANGEL OSWALDO</t>
-  </si>
-  <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>YOSGART</t>
-  </si>
-  <si>
-    <t>KEVIN ZAID</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>BRAYAN JOSUE</t>
-  </si>
-  <si>
     <t>KIMBERLY ALISON</t>
   </si>
   <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
     <t>SANDRA GABRIELA</t>
+  </si>
+  <si>
+    <t>ERIC ELIU</t>
   </si>
   <si>
     <t>ARANZI</t>
@@ -930,16 +849,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>4.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -953,16 +875,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>35.29</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1110,16 +1035,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>28.21</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1136,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1259,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1291,22 +1216,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920142</v>
+        <v>24330051920308</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1314,22 +1239,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920313</v>
+        <v>24330051920170</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1337,22 +1262,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920152</v>
+        <v>24330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1360,22 +1285,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920144</v>
+        <v>24330051920182</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1383,22 +1308,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920122</v>
+        <v>24330051920206</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1406,16 +1331,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920308</v>
+        <v>24330051920277</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1429,22 +1354,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920298</v>
+        <v>24330051920266</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1452,22 +1377,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920188</v>
+        <v>24330051920270</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1475,22 +1400,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920265</v>
+        <v>23330051920285</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1498,22 +1423,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920255</v>
+        <v>23330051920294</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1521,22 +1446,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920266</v>
+        <v>23330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1544,22 +1469,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920270</v>
+        <v>23330051920319</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1567,22 +1492,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920295</v>
+        <v>23330051920339</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1590,16 +1515,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920319</v>
+        <v>23330051920289</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1613,16 +1538,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920339</v>
+        <v>23330051920303</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1636,68 +1561,68 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920289</v>
+        <v>24330051920265</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920303</v>
+        <v>24330051920311</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920131</v>
+        <v>24330051920282</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1705,22 +1630,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920303</v>
+        <v>24330051920321</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1728,22 +1653,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920148</v>
+        <v>24330051920285</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1751,277 +1676,24 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920300</v>
+        <v>24330051920290</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920170</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920174</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920182</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920206</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920190</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920402</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>24330051920311</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>24330051920262</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>24330051920282</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>24330051920285</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>24330051920290</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -106,48 +103,24 @@
     <t>MOTA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
     <t>IBARRA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>NIETO</t>
   </si>
   <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ABURTO</t>
-  </si>
-  <si>
-    <t>CESMA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -163,60 +136,39 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>ZAYAS</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>VAS</t>
-  </si>
-  <si>
     <t>SALMERON</t>
   </si>
   <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>CORDERO</t>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
-  </si>
-  <si>
     <t>GAEL ARMANDO</t>
   </si>
   <si>
     <t>ANGEL OSWALDO</t>
   </si>
   <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
@@ -226,31 +178,13 @@
     <t>ARMANDO</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
     <t>PAOLA</t>
   </si>
   <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
     <t>NOHEMI ANGELICA</t>
   </si>
   <si>
-    <t>ROSMELY LEILANI</t>
-  </si>
-  <si>
     <t>KIMBERLY ALISON</t>
-  </si>
-  <si>
-    <t>SANDRA GABRIELA</t>
-  </si>
-  <si>
-    <t>ERIC ELIU</t>
-  </si>
-  <si>
-    <t>ARANZI</t>
   </si>
   <si>
     <t>JESUS FABIAN</t>
@@ -901,16 +835,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>43.48</v>
+      </c>
+      <c r="H4">
+        <v>5.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -924,16 +861,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H5">
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -947,16 +887,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>63.16</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -970,16 +913,19 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1087,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>34.78</v>
+        <v>43.48</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1113,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1148,7 +1094,7 @@
         <v>63.16</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1165,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1216,16 +1162,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920308</v>
+        <v>24330051920170</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1239,16 +1185,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920170</v>
+        <v>24330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1262,16 +1208,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920174</v>
+        <v>24330051920182</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1285,16 +1231,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920182</v>
+        <v>24330051920206</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1308,16 +1254,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920206</v>
+        <v>24330051920277</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1331,22 +1277,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920277</v>
+        <v>24330051920266</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1354,22 +1300,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920266</v>
+        <v>23330051920285</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1377,22 +1323,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920270</v>
+        <v>23330051920294</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1400,16 +1346,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920285</v>
+        <v>23330051920295</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1423,22 +1369,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920294</v>
+        <v>23330051920339</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1446,22 +1392,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920295</v>
+        <v>23330051920303</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1469,231 +1415,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920319</v>
+        <v>24330051920311</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920339</v>
+        <v>24330051920290</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920289</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920303</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920265</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920311</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920282</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920321</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920285</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920290</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -88,24 +88,21 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>IBARRA</t>
   </si>
   <si>
@@ -121,12 +118,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -152,12 +143,6 @@
   </si>
   <si>
     <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
   </si>
   <si>
     <t>SANTIAGO</t>
@@ -1130,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,7 +1156,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1185,16 +1170,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920174</v>
+        <v>24330051920206</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1208,16 +1193,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920182</v>
+        <v>24330051920277</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1231,22 +1216,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920206</v>
+        <v>24330051920266</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1254,22 +1239,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920277</v>
+        <v>23330051920285</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1277,22 +1262,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920266</v>
+        <v>23330051920294</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1300,16 +1285,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920285</v>
+        <v>23330051920295</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1323,22 +1308,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920294</v>
+        <v>23330051920339</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1346,22 +1331,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920295</v>
+        <v>23330051920303</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1369,93 +1354,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920339</v>
+        <v>24330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920303</v>
+        <v>24330051920290</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920311</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920290</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,12 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
@@ -97,12 +103,21 @@
     <t>MOTA</t>
   </si>
   <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>PELAYO</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>IBARRA</t>
   </si>
   <si>
@@ -112,10 +127,10 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>VEGA</t>
@@ -127,24 +142,36 @@
     <t>PALACIOS</t>
   </si>
   <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>SALMERON</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>ZAYAS</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>SALMERON</t>
-  </si>
-  <si>
     <t>LIA SARED</t>
   </si>
   <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -154,6 +181,18 @@
     <t>ANGEL OSWALDO</t>
   </si>
   <si>
+    <t>JOSE MARCOS</t>
+  </si>
+  <si>
+    <t>IVAN JESUS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALISON</t>
+  </si>
+  <si>
+    <t>JESUS FABIAN</t>
+  </si>
+  <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
@@ -167,12 +206,6 @@
   </si>
   <si>
     <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALISON</t>
-  </si>
-  <si>
-    <t>JESUS FABIAN</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,7 +1189,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,16 +1203,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920206</v>
+        <v>24330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1193,16 +1226,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920277</v>
+        <v>24330051920182</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1216,22 +1249,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920266</v>
+        <v>24330051920206</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1239,22 +1272,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920285</v>
+        <v>24330051920277</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1262,22 +1295,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920294</v>
+        <v>24330051920266</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1285,16 +1318,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920295</v>
+        <v>23330051920317</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1308,22 +1341,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920339</v>
+        <v>23330051920309</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1331,45 +1364,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920303</v>
+        <v>24330051920311</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920311</v>
+        <v>24330051920290</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1377,24 +1410,116 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920290</v>
+        <v>23330051920285</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920294</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920295</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920339</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920303</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="129">
   <si>
     <t>Mat</t>
   </si>
@@ -85,15 +85,87 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
@@ -127,6 +199,63 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -145,24 +274,96 @@
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>SALMERON</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ZAYAS</t>
   </si>
   <si>
     <t>RIOS</t>
   </si>
   <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
+  </si>
+  <si>
     <t>LIA SARED</t>
   </si>
   <si>
@@ -170,9 +371,6 @@
   </si>
   <si>
     <t>AMISADAY</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GAEL ARMANDO</t>
@@ -1148,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1180,108 +1378,108 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920170</v>
+        <v>24330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920174</v>
+        <v>24330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920182</v>
+        <v>24330051920410</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920206</v>
+        <v>24330051920143</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920277</v>
+        <v>24330051920400</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1290,236 +1488,857 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920266</v>
+        <v>24330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920317</v>
+        <v>24330051920187</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920309</v>
+        <v>24330051920201</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920311</v>
+        <v>24330051920194</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920290</v>
+        <v>24330051920202</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920285</v>
+        <v>24330051920274</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920294</v>
+        <v>24330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920295</v>
+        <v>24330051920369</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920339</v>
+        <v>24330051920283</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>23330051920312</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920301</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920098</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920155</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920315</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920308</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920179</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920388</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920298</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920188</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920255</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920390</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920262</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920174</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920182</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920206</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920277</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>24330051920266</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920317</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920309</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920311</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920290</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920285</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920294</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>23330051920295</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>23330051920339</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
         <v>23330051920303</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" t="s">
         <v>9</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F43" t="s">
         <v>15</v>
       </c>
-      <c r="G16">
+      <c r="G43">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
   <si>
     <t>SANDRA GABRIELA</t>
@@ -1043,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,47 +1066,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920101</v>
+        <v>24330051920282</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>24330051920282</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>
